--- a/requirements/OntologyRequirements.xlsx
+++ b/requirements/OntologyRequirements.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="OntologyRequirementsTemplate (1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'OntologyRequirementsTemplate (1'!$A$1:$H$27</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'OntologyRequirementsTemplate (1'!$A$1:$H$29</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="93">
   <si>
     <t>Identifier</t>
   </si>
@@ -124,7 +124,13 @@
     <t>MovieR2</t>
   </si>
   <si>
-    <t xml:space="preserve">How popular is the movie? </t>
+    <t>How popular is the movie?</t>
+  </si>
+  <si>
+    <t>The value of “popularity” (integer)</t>
+  </si>
+  <si>
+    <t>based on the number of views per day, votes per day, number of users marked it as "favorite" and "watchlist"</t>
   </si>
   <si>
     <t>MovieR3</t>
@@ -133,64 +139,91 @@
     <t>Total votes received from the viewers.</t>
   </si>
   <si>
+    <t>The value of “Vote_Count “ (Integer)</t>
+  </si>
+  <si>
     <t>MovieR4</t>
   </si>
   <si>
     <t>Average rating based on vote count and the number of viewers out of 10.</t>
   </si>
   <si>
+    <t>the value is a number integer from 1 to 10 of ” Vote_Average”</t>
+  </si>
+  <si>
     <t>MovieR5</t>
   </si>
   <si>
     <t>Original language of the movies. Dubbed version is not considered to be original language.</t>
   </si>
   <si>
+    <t>The value of “Original_Language” (String)</t>
+  </si>
+  <si>
     <t>MovieR6</t>
   </si>
   <si>
     <t>Url of the movie poster.</t>
   </si>
   <si>
+    <t>The value of “Poster_Url” (String)</t>
+  </si>
+  <si>
+    <t>MovieR7</t>
+  </si>
+  <si>
+    <t>What are the genres of the movie?</t>
+  </si>
+  <si>
+    <t>The values of the "genre" atrribute (Array of strings)</t>
+  </si>
+  <si>
     <t>MovieR8</t>
   </si>
   <si>
-    <t>What are the genres of the movie?</t>
-  </si>
-  <si>
-    <t>The values of the "genre" atrribute (Array of strings)</t>
+    <t>Who are the directors of the movie?</t>
+  </si>
+  <si>
+    <t>The value of the attribute "name" in the field "director" (String)</t>
   </si>
   <si>
     <t>MovieR9</t>
   </si>
   <si>
-    <t>Who are the directors of the movie?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The value of the attribute "name" in the field "director" (String) </t>
+    <t>Who are the actos participated in the movie?</t>
+  </si>
+  <si>
+    <t>The values of the attribute "name" in the field of "all_actors" (Array of strings)</t>
   </si>
   <si>
     <t>MovieR10</t>
   </si>
   <si>
-    <t>Who are the actos participated in the movie?</t>
-  </si>
-  <si>
-    <t>The values of the attribute "name" in the field of "all_actors" (Array of strings)</t>
+    <t>Date when the movie was released.</t>
+  </si>
+  <si>
+    <t>The value of the atrribute "year" (Integer)</t>
   </si>
   <si>
     <t>MovieR11</t>
   </si>
   <si>
-    <t>Date when the movie was released.</t>
-  </si>
-  <si>
-    <t>The value of the atrribute "year" (Integer)</t>
+    <t>Written analyses of the films that share thoughts and observations.</t>
+  </si>
+  <si>
+    <t>The value of “reviews” (String)</t>
   </si>
   <si>
     <t>MovieR12</t>
   </si>
   <si>
-    <t>Movie Reviews,comments and opinions</t>
+    <t>Each description expresses an emotional tone.</t>
+  </si>
+  <si>
+    <t>the value of “Emotions” (String)</t>
+  </si>
+  <si>
+    <t>sadness,anticipation,joy,fear,optimism</t>
   </si>
   <si>
     <t>MovieR13</t>
@@ -199,6 +232,9 @@
     <t>Brief summary of the movie.</t>
   </si>
   <si>
+    <t>The value of “Overview” (String)</t>
+  </si>
+  <si>
     <t>MovieR14</t>
   </si>
   <si>
@@ -215,6 +251,15 @@
   </si>
   <si>
     <t>The value of the "adjusted_budget" attribute (Integer)</t>
+  </si>
+  <si>
+    <t>MovieR16</t>
+  </si>
+  <si>
+    <t>What is the movie duration?</t>
+  </si>
+  <si>
+    <t>The value of “duration” in minutes (Integer)</t>
   </si>
   <si>
     <t>ProducerR1</t>
@@ -254,7 +299,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -264,6 +309,11 @@
     <font>
       <b/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -293,7 +343,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -302,7 +352,10 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -588,6 +641,7 @@
       <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
@@ -619,6 +673,7 @@
       <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E4" s="4"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
@@ -633,6 +688,7 @@
       <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
@@ -647,6 +703,7 @@
       <c r="D6" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E6" s="4"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
@@ -661,6 +718,7 @@
       <c r="D7" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E7" s="4"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
@@ -675,6 +733,7 @@
       <c r="D8" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E8" s="4"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
@@ -689,6 +748,7 @@
       <c r="D9" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E9" s="4"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
@@ -703,6 +763,7 @@
       <c r="D10" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E10" s="4"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
@@ -711,220 +772,292 @@
       <c r="B11" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="C11" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="D11" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E13" s="4"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E14" s="4"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E15" s="4"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E16" s="4"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E17" s="4"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E18" s="4"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E19" s="4"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E20" s="4"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E22" s="4"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E23" s="4"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E24" s="4"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E25" s="4"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="E26" s="4"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="D29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$H$27">
-    <sortState ref="A1:H27">
-      <sortCondition ref="A1:A27"/>
+  <autoFilter ref="$A$1:$H$29">
+    <sortState ref="A1:H29">
+      <sortCondition ref="A1:A29"/>
     </sortState>
   </autoFilter>
   <drawing r:id="rId1"/>
